--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI286"/>
+  <dimension ref="A1:AI288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.95</v>
+        <v>2.42</v>
       </c>
       <c r="M124" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="N124" t="n">
-        <v>2.07</v>
+        <v>2.94</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16299,10 +16299,10 @@
         <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,22 +18235,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,22 +20377,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,22 +20972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,22 +22638,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.41</v>
+        <v>1.76</v>
       </c>
       <c r="M189" t="n">
-        <v>3.16</v>
+        <v>3.74</v>
       </c>
       <c r="N189" t="n">
-        <v>2.97</v>
+        <v>4.3</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3.32</v>
+        <v>2.21</v>
       </c>
       <c r="M193" t="n">
-        <v>3.54</v>
+        <v>3.14</v>
       </c>
       <c r="N193" t="n">
-        <v>2.07</v>
+        <v>3.37</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.76</v>
+        <v>3.32</v>
       </c>
       <c r="M194" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="N194" t="n">
-        <v>4.3</v>
+        <v>2.07</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="M203" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N203" t="n">
-        <v>4.27</v>
+        <v>2.57</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="M211" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="N211" t="n">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26658,10 +26658,10 @@
         <v>0</v>
       </c>
       <c r="AE220" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF220" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29892,12 +29892,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30002,7 +30002,7 @@
         <v>0</v>
       </c>
       <c r="AI248" s="3" t="n">
-        <v>46089.67708333334</v>
+        <v>46089.66666666666</v>
       </c>
     </row>
     <row r="249">
@@ -30011,12 +30011,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30121,7 +30121,7 @@
         <v>0</v>
       </c>
       <c r="AI249" s="3" t="n">
-        <v>46089.6875</v>
+        <v>46089.67708333334</v>
       </c>
     </row>
     <row r="250">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="AI251" s="3" t="n">
-        <v>46089.69791666666</v>
+        <v>46089.6875</v>
       </c>
     </row>
     <row r="252">
@@ -30487,12 +30487,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30597,7 +30597,7 @@
         <v>0</v>
       </c>
       <c r="AI253" s="3" t="n">
-        <v>46089.70833333334</v>
+        <v>46089.69791666666</v>
       </c>
     </row>
     <row r="254">
@@ -30611,22 +30611,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31920,7 +31920,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L265" t="n">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L266" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33023,7 +33023,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L274" t="n">
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33499,7 +33499,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L278" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34181,22 +34181,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34295,27 +34295,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34405,7 +34405,7 @@
         <v>0</v>
       </c>
       <c r="AI285" s="3" t="n">
-        <v>46089.89583333334</v>
+        <v>46089.875</v>
       </c>
     </row>
     <row r="286">
@@ -34525,6 +34525,244 @@
       </c>
       <c r="AI286" s="3" t="n">
         <v>46089.89583333334</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="n">
+        <v>0</v>
+      </c>
+      <c r="T287" t="n">
+        <v>0</v>
+      </c>
+      <c r="U287" t="n">
+        <v>0</v>
+      </c>
+      <c r="V287" t="n">
+        <v>0</v>
+      </c>
+      <c r="W287" t="n">
+        <v>0</v>
+      </c>
+      <c r="X287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI287" s="3" t="n">
+        <v>46089.89583333334</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes II</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Los Angeles II</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="n">
+        <v>0</v>
+      </c>
+      <c r="T288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="n">
+        <v>0</v>
+      </c>
+      <c r="V288" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" t="n">
+        <v>0</v>
+      </c>
+      <c r="X288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI288" s="3" t="n">
+        <v>46089.95833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI288"/>
+  <dimension ref="A1:AI290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -781,10 +781,10 @@
         <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -900,10 +900,10 @@
         <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8213,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>46089.41666666666</v>
+        <v>46089.42708333334</v>
       </c>
     </row>
     <row r="101">
@@ -12399,12 +12399,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12509,7 +12509,7 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3" t="n">
-        <v>46089.42708333334</v>
+        <v>46089.4375</v>
       </c>
     </row>
     <row r="102">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.12</v>
+        <v>4.27</v>
       </c>
       <c r="M110" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N110" t="n">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46089.4375</v>
+        <v>46089.44791666666</v>
       </c>
     </row>
     <row r="112">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46089.44791666666</v>
+        <v>46089.45833333334</v>
       </c>
     </row>
     <row r="114">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16067,10 +16067,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16207,12 +16207,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16299,10 +16299,10 @@
         <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="AI133" s="3" t="n">
-        <v>46089.45833333334</v>
+        <v>46089.47916666666</v>
       </c>
     </row>
     <row r="134">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16683,12 +16683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46089.47916666666</v>
+        <v>46089.5</v>
       </c>
     </row>
     <row r="138">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,22 +17521,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,22 +18235,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,22 +20377,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,22 +20972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21324,12 +21324,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>46089.51041666666</v>
+        <v>46089.5</v>
       </c>
     </row>
     <row r="177">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21681,12 +21681,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>46089.52083333334</v>
+        <v>46089.51041666666</v>
       </c>
     </row>
     <row r="180">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22276,12 +22276,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
         <v>0</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>46089.53125</v>
+        <v>46089.52083333334</v>
       </c>
     </row>
     <row r="185">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22743,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="AI187" s="3" t="n">
-        <v>46089.54166666666</v>
+        <v>46089.53125</v>
       </c>
     </row>
     <row r="188">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3.32</v>
+        <v>1.76</v>
       </c>
       <c r="M194" t="n">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="N194" t="n">
-        <v>2.07</v>
+        <v>4.3</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,22 +23709,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="M198" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="N198" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="M199" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="N199" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,22 +24423,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24537,12 +24537,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="M203" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="N203" t="n">
-        <v>2.57</v>
+        <v>2.07</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24647,7 +24647,7 @@
         <v>0</v>
       </c>
       <c r="AI203" s="3" t="n">
-        <v>46089.55208333334</v>
+        <v>46089.54166666666</v>
       </c>
     </row>
     <row r="204">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="M204" t="n">
-        <v>3.66</v>
+        <v>4.17</v>
       </c>
       <c r="N204" t="n">
-        <v>4.27</v>
+        <v>5.28</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="M205" t="n">
-        <v>4.17</v>
+        <v>3.56</v>
       </c>
       <c r="N205" t="n">
-        <v>5.28</v>
+        <v>2.57</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25013,12 +25013,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25123,7 +25123,7 @@
         <v>0</v>
       </c>
       <c r="AI207" s="3" t="n">
-        <v>46089.5625</v>
+        <v>46089.55208333334</v>
       </c>
     </row>
     <row r="208">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26194,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="AI216" s="3" t="n">
-        <v>46089.57291666666</v>
+        <v>46089.5625</v>
       </c>
     </row>
     <row r="217">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26322,12 +26322,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26432,7 +26432,7 @@
         <v>0</v>
       </c>
       <c r="AI218" s="3" t="n">
-        <v>46089.58333333334</v>
+        <v>46089.57291666666</v>
       </c>
     </row>
     <row r="219">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF221" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27015,10 +27015,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF223" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27155,27 +27155,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27265,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="AI225" s="3" t="n">
-        <v>46089.59375</v>
+        <v>46089.58333333334</v>
       </c>
     </row>
     <row r="226">
@@ -27274,12 +27274,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27384,7 +27384,7 @@
         <v>0</v>
       </c>
       <c r="AI226" s="3" t="n">
-        <v>46089.60416666666</v>
+        <v>46089.58333333334</v>
       </c>
     </row>
     <row r="227">
@@ -27393,27 +27393,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27503,7 +27503,7 @@
         <v>0</v>
       </c>
       <c r="AI227" s="3" t="n">
-        <v>46089.60416666666</v>
+        <v>46089.59375</v>
       </c>
     </row>
     <row r="228">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28345,12 +28345,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28455,7 +28455,7 @@
         <v>0</v>
       </c>
       <c r="AI235" s="3" t="n">
-        <v>46089.625</v>
+        <v>46089.60416666666</v>
       </c>
     </row>
     <row r="236">
@@ -28464,12 +28464,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28574,7 +28574,7 @@
         <v>0</v>
       </c>
       <c r="AI236" s="3" t="n">
-        <v>46089.625</v>
+        <v>46089.60416666666</v>
       </c>
     </row>
     <row r="237">
@@ -28583,12 +28583,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28693,7 +28693,7 @@
         <v>0</v>
       </c>
       <c r="AI237" s="3" t="n">
-        <v>46089.63541666666</v>
+        <v>46089.625</v>
       </c>
     </row>
     <row r="238">
@@ -28702,12 +28702,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28812,7 +28812,7 @@
         <v>0</v>
       </c>
       <c r="AI238" s="3" t="n">
-        <v>46089.63541666666</v>
+        <v>46089.625</v>
       </c>
     </row>
     <row r="239">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28940,27 +28940,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29050,7 +29050,7 @@
         <v>0</v>
       </c>
       <c r="AI240" s="3" t="n">
-        <v>46089.64583333334</v>
+        <v>46089.63541666666</v>
       </c>
     </row>
     <row r="241">
@@ -29059,12 +29059,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29169,7 +29169,7 @@
         <v>0</v>
       </c>
       <c r="AI241" s="3" t="n">
-        <v>46089.64583333334</v>
+        <v>46089.63541666666</v>
       </c>
     </row>
     <row r="242">
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29297,27 +29297,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29407,7 +29407,7 @@
         <v>0</v>
       </c>
       <c r="AI243" s="3" t="n">
-        <v>46089.66666666666</v>
+        <v>46089.64583333334</v>
       </c>
     </row>
     <row r="244">
@@ -29416,27 +29416,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="AI244" s="3" t="n">
-        <v>46089.66666666666</v>
+        <v>46089.64583333334</v>
       </c>
     </row>
     <row r="245">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30011,27 +30011,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30121,7 +30121,7 @@
         <v>0</v>
       </c>
       <c r="AI249" s="3" t="n">
-        <v>46089.67708333334</v>
+        <v>46089.66666666666</v>
       </c>
     </row>
     <row r="250">
@@ -30130,12 +30130,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30240,7 +30240,7 @@
         <v>0</v>
       </c>
       <c r="AI250" s="3" t="n">
-        <v>46089.6875</v>
+        <v>46089.66666666666</v>
       </c>
     </row>
     <row r="251">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="AI251" s="3" t="n">
-        <v>46089.6875</v>
+        <v>46089.67708333334</v>
       </c>
     </row>
     <row r="252">
@@ -30368,12 +30368,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30466,10 +30466,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF252" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -30478,7 +30478,7 @@
         <v>0</v>
       </c>
       <c r="AI252" s="3" t="n">
-        <v>46089.69791666666</v>
+        <v>46089.6875</v>
       </c>
     </row>
     <row r="253">
@@ -30487,12 +30487,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30597,7 +30597,7 @@
         <v>0</v>
       </c>
       <c r="AI253" s="3" t="n">
-        <v>46089.69791666666</v>
+        <v>46089.6875</v>
       </c>
     </row>
     <row r="254">
@@ -30606,12 +30606,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30692,10 +30692,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB254" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -30716,7 +30716,7 @@
         <v>0</v>
       </c>
       <c r="AI254" s="3" t="n">
-        <v>46089.70833333334</v>
+        <v>46089.69791666666</v>
       </c>
     </row>
     <row r="255">
@@ -30725,12 +30725,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30811,10 +30811,10 @@
         <v>0</v>
       </c>
       <c r="AA255" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB255" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC255" t="n">
         <v>0</v>
@@ -30823,10 +30823,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF255" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -30835,7 +30835,7 @@
         <v>0</v>
       </c>
       <c r="AI255" s="3" t="n">
-        <v>46089.70833333334</v>
+        <v>46089.69791666666</v>
       </c>
     </row>
     <row r="256">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L256" t="n">
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -31201,27 +31201,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31311,7 +31311,7 @@
         <v>0</v>
       </c>
       <c r="AI259" s="3" t="n">
-        <v>46089.72916666666</v>
+        <v>46089.70833333334</v>
       </c>
     </row>
     <row r="260">
@@ -31320,12 +31320,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31430,7 +31430,7 @@
         <v>0</v>
       </c>
       <c r="AI260" s="3" t="n">
-        <v>46089.72916666666</v>
+        <v>46089.70833333334</v>
       </c>
     </row>
     <row r="261">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31915,27 +31915,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31952,7 +31952,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L265" t="n">
@@ -32025,7 +32025,7 @@
         <v>0</v>
       </c>
       <c r="AI265" s="3" t="n">
-        <v>46089.75</v>
+        <v>46089.72916666666</v>
       </c>
     </row>
     <row r="266">
@@ -32034,12 +32034,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32144,7 +32144,7 @@
         <v>0</v>
       </c>
       <c r="AI266" s="3" t="n">
-        <v>46089.75</v>
+        <v>46089.72916666666</v>
       </c>
     </row>
     <row r="267">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32428,7 +32428,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32629,27 +32629,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32739,7 +32739,7 @@
         <v>0</v>
       </c>
       <c r="AI271" s="3" t="n">
-        <v>46089.79166666666</v>
+        <v>46089.75</v>
       </c>
     </row>
     <row r="272">
@@ -32748,27 +32748,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="AI272" s="3" t="n">
-        <v>46089.79166666666</v>
+        <v>46089.75</v>
       </c>
     </row>
     <row r="273">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33023,7 +33023,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L274" t="n">
@@ -33110,22 +33110,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33224,27 +33224,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33334,7 +33334,7 @@
         <v>0</v>
       </c>
       <c r="AI276" s="3" t="n">
-        <v>46089.83333333334</v>
+        <v>46089.79166666666</v>
       </c>
     </row>
     <row r="277">
@@ -33343,7 +33343,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33453,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="AI277" s="3" t="n">
-        <v>46089.83333333334</v>
+        <v>46089.79166666666</v>
       </c>
     </row>
     <row r="278">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L280" t="n">
@@ -33819,12 +33819,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33929,7 +33929,7 @@
         <v>0</v>
       </c>
       <c r="AI281" s="3" t="n">
-        <v>46089.85416666666</v>
+        <v>46089.83333333334</v>
       </c>
     </row>
     <row r="282">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34048,7 +34048,7 @@
         <v>0</v>
       </c>
       <c r="AI282" s="3" t="n">
-        <v>46089.875</v>
+        <v>46089.83333333334</v>
       </c>
     </row>
     <row r="283">
@@ -34057,27 +34057,27 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34167,7 +34167,7 @@
         <v>0</v>
       </c>
       <c r="AI283" s="3" t="n">
-        <v>46089.875</v>
+        <v>46089.85416666666</v>
       </c>
     </row>
     <row r="284">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34414,12 +34414,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34524,7 +34524,7 @@
         <v>0</v>
       </c>
       <c r="AI286" s="3" t="n">
-        <v>46089.89583333334</v>
+        <v>46089.875</v>
       </c>
     </row>
     <row r="287">
@@ -34533,7 +34533,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34643,7 +34643,7 @@
         <v>0</v>
       </c>
       <c r="AI287" s="3" t="n">
-        <v>46089.89583333334</v>
+        <v>46089.875</v>
       </c>
     </row>
     <row r="288">
@@ -34652,116 +34652,354 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="n">
+        <v>0</v>
+      </c>
+      <c r="T288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="n">
+        <v>0</v>
+      </c>
+      <c r="V288" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" t="n">
+        <v>0</v>
+      </c>
+      <c r="X288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI288" s="3" t="n">
+        <v>46089.89583333334</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
+        <v>0</v>
+      </c>
+      <c r="T289" t="n">
+        <v>0</v>
+      </c>
+      <c r="U289" t="n">
+        <v>0</v>
+      </c>
+      <c r="V289" t="n">
+        <v>0</v>
+      </c>
+      <c r="W289" t="n">
+        <v>0</v>
+      </c>
+      <c r="X289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI289" s="3" t="n">
+        <v>46089.89583333334</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C290" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D290" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E290" t="inlineStr">
         <is>
           <t>San Jose Earthquakes II</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F290" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="G288" t="n">
-        <v>0</v>
-      </c>
-      <c r="H288" t="n">
-        <v>0</v>
-      </c>
-      <c r="I288" t="n">
-        <v>0</v>
-      </c>
-      <c r="J288" t="n">
-        <v>0</v>
-      </c>
-      <c r="K288" t="inlineStr">
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L288" t="n">
-        <v>0</v>
-      </c>
-      <c r="M288" t="n">
-        <v>0</v>
-      </c>
-      <c r="N288" t="n">
-        <v>0</v>
-      </c>
-      <c r="O288" t="n">
-        <v>0</v>
-      </c>
-      <c r="P288" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
-      <c r="R288" t="n">
-        <v>0</v>
-      </c>
-      <c r="S288" t="n">
-        <v>0</v>
-      </c>
-      <c r="T288" t="n">
-        <v>0</v>
-      </c>
-      <c r="U288" t="n">
-        <v>0</v>
-      </c>
-      <c r="V288" t="n">
-        <v>0</v>
-      </c>
-      <c r="W288" t="n">
-        <v>0</v>
-      </c>
-      <c r="X288" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y288" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH288" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI288" s="3" t="n">
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="n">
+        <v>0</v>
+      </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI290" s="3" t="n">
         <v>46089.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -781,10 +781,10 @@
         <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,22 +6216,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14758,10 +14758,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16067,10 +16067,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,22 +17640,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,22 +23233,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.76</v>
+        <v>2.41</v>
       </c>
       <c r="M194" t="n">
-        <v>3.74</v>
+        <v>3.16</v>
       </c>
       <c r="N194" t="n">
-        <v>4.3</v>
+        <v>2.97</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="M195" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="N195" t="n">
-        <v>3.37</v>
+        <v>3.6</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,22 +23709,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="M197" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="N197" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.41</v>
+        <v>1.76</v>
       </c>
       <c r="M198" t="n">
-        <v>3.16</v>
+        <v>3.74</v>
       </c>
       <c r="N198" t="n">
-        <v>2.97</v>
+        <v>4.3</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="M204" t="n">
-        <v>4.17</v>
+        <v>3.66</v>
       </c>
       <c r="N204" t="n">
-        <v>5.28</v>
+        <v>4.27</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="M206" t="n">
-        <v>3.66</v>
+        <v>4.17</v>
       </c>
       <c r="N206" t="n">
-        <v>4.27</v>
+        <v>5.28</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27015,10 +27015,10 @@
         <v>0</v>
       </c>
       <c r="AE223" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF223" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27372,10 +27372,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF226" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32309,7 +32309,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32428,7 +32428,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L269" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L280" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,22 +34538,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G287" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N61" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8213,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="M118" t="n">
-        <v>4.19</v>
+        <v>3.7</v>
       </c>
       <c r="N118" t="n">
-        <v>7.01</v>
+        <v>4.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,22 +14508,22 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB118" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE118" t="n">
-        <v>0</v>
-      </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14758,10 +14758,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.42</v>
+        <v>1.28</v>
       </c>
       <c r="M124" t="n">
-        <v>2.9</v>
+        <v>6.71</v>
       </c>
       <c r="N124" t="n">
-        <v>2.94</v>
+        <v>11.6</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,22 +17521,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G277" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9516,10 +9516,10 @@
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14520,10 +14520,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15353,10 +15353,10 @@
         <v>0</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,22 +17759,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="M193" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="N193" t="n">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.41</v>
+        <v>3.32</v>
       </c>
       <c r="M194" t="n">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
       <c r="N194" t="n">
-        <v>2.97</v>
+        <v>2.07</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="M197" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="N197" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="M198" t="n">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="N198" t="n">
-        <v>4.3</v>
+        <v>3.09</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.18</v>
+        <v>3.34</v>
       </c>
       <c r="M211" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N211" t="n">
-        <v>3.66</v>
+        <v>2.02</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>3.34</v>
+        <v>2.29</v>
       </c>
       <c r="M216" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="N216" t="n">
-        <v>2.02</v>
+        <v>3.26</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26896,10 +26896,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF222" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27372,10 +27372,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF226" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28431,10 +28431,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC235" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30849,22 +30849,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L257" t="n">
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32309,7 +32309,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33261,7 +33261,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L282" t="n">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34538,22 +34538,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,22 +34657,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,22 +34776,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G289" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -900,10 +900,10 @@
         <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,22 +9429,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9516,10 +9516,10 @@
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="M125" t="n">
-        <v>3.7</v>
+        <v>6.71</v>
       </c>
       <c r="N125" t="n">
-        <v>4.9</v>
+        <v>11.6</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,22 +15341,22 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15472,10 +15472,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,22 +18949,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,22 +19425,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="M189" t="n">
-        <v>3.74</v>
+        <v>3.18</v>
       </c>
       <c r="N189" t="n">
-        <v>4.3</v>
+        <v>3.09</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,22 +23233,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,22 +3241,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="M69" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>5.12</v>
+        <v>3.61</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,22 +9429,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="M81" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N81" t="n">
-        <v>3.3</v>
+        <v>6.54</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -10143,22 +10143,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14877,10 +14877,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15472,10 +15472,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,22 +19187,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="M195" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="N195" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23671,10 +23671,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB195" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,22 +23828,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28431,10 +28431,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC235" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB266" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32634,22 +32634,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33229,22 +33229,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33261,7 +33261,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L276" t="n">
@@ -33348,22 +33348,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L282" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.71</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>3.48</v>
+        <v>1.94</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,22 +6573,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8213,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="M78" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10619,22 +10619,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.12</v>
+        <v>4.27</v>
       </c>
       <c r="M102" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N102" t="n">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4.27</v>
+        <v>2.12</v>
       </c>
       <c r="M104" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="N104" t="n">
-        <v>1.82</v>
+        <v>3.45</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="M117" t="n">
-        <v>4.19</v>
+        <v>3.59</v>
       </c>
       <c r="N117" t="n">
-        <v>7.01</v>
+        <v>2.07</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14877,10 +14877,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15234,10 +15234,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15347,10 +15347,10 @@
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,22 +18830,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,22 +19187,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="M195" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="N195" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23671,10 +23671,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB195" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,22 +23828,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI290"/>
+  <dimension ref="A1:AI288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -662,10 +662,10 @@
         <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,22 +3360,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,22 +6573,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N64" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8213,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.91</v>
+        <v>5.1</v>
       </c>
       <c r="M76" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3</v>
+        <v>1.51</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>5.1</v>
+        <v>1.91</v>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N78" t="n">
-        <v>1.51</v>
+        <v>3.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9992,10 +9992,10 @@
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N90" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12152,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
-        <v>46089.41666666666</v>
+        <v>46089.42708333334</v>
       </c>
     </row>
     <row r="99">
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="AI99" s="3" t="n">
-        <v>46089.41666666666</v>
+        <v>46089.4375</v>
       </c>
     </row>
     <row r="100">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
-        <v>46089.42708333334</v>
+        <v>46089.4375</v>
       </c>
     </row>
     <row r="101">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="M104" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="N104" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46089.4375</v>
+        <v>46089.44791666666</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46089.4375</v>
+        <v>46089.44791666666</v>
       </c>
     </row>
     <row r="111">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="AI111" s="3" t="n">
-        <v>46089.44791666666</v>
+        <v>46089.45833333334</v>
       </c>
     </row>
     <row r="112">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46089.44791666666</v>
+        <v>46089.45833333334</v>
       </c>
     </row>
     <row r="113">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15234,10 +15234,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15969,27 +15969,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46089.45833333334</v>
+        <v>46089.47916666666</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46089.45833333334</v>
+        <v>46089.47916666666</v>
       </c>
     </row>
     <row r="133">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16445,12 +16445,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16555,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AI135" s="3" t="n">
-        <v>46089.47916666666</v>
+        <v>46089.5</v>
       </c>
     </row>
     <row r="136">
@@ -16564,27 +16564,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16674,7 +16674,7 @@
         <v>0</v>
       </c>
       <c r="AI136" s="3" t="n">
-        <v>46089.47916666666</v>
+        <v>46089.5</v>
       </c>
     </row>
     <row r="137">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21205,12 +21205,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21315,7 +21315,7 @@
         <v>0</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>46089.5</v>
+        <v>46089.51041666666</v>
       </c>
     </row>
     <row r="176">
@@ -21324,12 +21324,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>46089.5</v>
+        <v>46089.51041666666</v>
       </c>
     </row>
     <row r="177">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>46089.51041666666</v>
+        <v>46089.52083333334</v>
       </c>
     </row>
     <row r="179">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>46089.51041666666</v>
+        <v>46089.52083333334</v>
       </c>
     </row>
     <row r="180">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.45</v>
+        <v>4.14</v>
       </c>
       <c r="M180" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="N180" t="n">
-        <v>6.9</v>
+        <v>1.98</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22157,12 +22157,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22267,7 +22267,7 @@
         <v>0</v>
       </c>
       <c r="AI183" s="3" t="n">
-        <v>46089.52083333334</v>
+        <v>46089.53125</v>
       </c>
     </row>
     <row r="184">
@@ -22276,12 +22276,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22386,7 +22386,7 @@
         <v>0</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>46089.52083333334</v>
+        <v>46089.53125</v>
       </c>
     </row>
     <row r="185">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22514,12 +22514,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22624,7 +22624,7 @@
         <v>0</v>
       </c>
       <c r="AI186" s="3" t="n">
-        <v>46089.53125</v>
+        <v>46089.54166666666</v>
       </c>
     </row>
     <row r="187">
@@ -22633,27 +22633,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.33</v>
+        <v>1.75</v>
       </c>
       <c r="M187" t="n">
-        <v>3.91</v>
+        <v>3.57</v>
       </c>
       <c r="N187" t="n">
-        <v>1.8</v>
+        <v>4.62</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -22743,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="AI187" s="3" t="n">
-        <v>46089.53125</v>
+        <v>46089.54166666666</v>
       </c>
     </row>
     <row r="188">
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.33</v>
+        <v>3.32</v>
       </c>
       <c r="M189" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="N189" t="n">
-        <v>3.09</v>
+        <v>2.07</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3.32</v>
+        <v>2.04</v>
       </c>
       <c r="M190" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="N190" t="n">
-        <v>2.07</v>
+        <v>3.6</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="M195" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="N195" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24418,12 +24418,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24528,7 +24528,7 @@
         <v>0</v>
       </c>
       <c r="AI202" s="3" t="n">
-        <v>46089.54166666666</v>
+        <v>46089.55208333334</v>
       </c>
     </row>
     <row r="203">
@@ -24537,12 +24537,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="M203" t="n">
-        <v>3.16</v>
+        <v>3.56</v>
       </c>
       <c r="N203" t="n">
-        <v>2.97</v>
+        <v>2.57</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24647,7 +24647,7 @@
         <v>0</v>
       </c>
       <c r="AI203" s="3" t="n">
-        <v>46089.54166666666</v>
+        <v>46089.55208333334</v>
       </c>
     </row>
     <row r="204">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="M205" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N205" t="n">
-        <v>2.57</v>
+        <v>4.27</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AB205" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24894,12 +24894,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25004,7 +25004,7 @@
         <v>0</v>
       </c>
       <c r="AI206" s="3" t="n">
-        <v>46089.55208333334</v>
+        <v>46089.5625</v>
       </c>
     </row>
     <row r="207">
@@ -25013,12 +25013,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25123,7 +25123,7 @@
         <v>0</v>
       </c>
       <c r="AI207" s="3" t="n">
-        <v>46089.55208333334</v>
+        <v>46089.5625</v>
       </c>
     </row>
     <row r="208">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="M212" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="N212" t="n">
-        <v>3.66</v>
+        <v>4.19</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25965,12 +25965,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26075,7 +26075,7 @@
         <v>0</v>
       </c>
       <c r="AI215" s="3" t="n">
-        <v>46089.5625</v>
+        <v>46089.57291666666</v>
       </c>
     </row>
     <row r="216">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26194,7 +26194,7 @@
         <v>0</v>
       </c>
       <c r="AI216" s="3" t="n">
-        <v>46089.5625</v>
+        <v>46089.57291666666</v>
       </c>
     </row>
     <row r="217">
@@ -26203,12 +26203,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="M217" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N217" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26301,10 +26301,10 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF217" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>
@@ -26313,7 +26313,7 @@
         <v>0</v>
       </c>
       <c r="AI217" s="3" t="n">
-        <v>46089.57291666666</v>
+        <v>46089.58333333334</v>
       </c>
     </row>
     <row r="218">
@@ -26322,12 +26322,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26432,7 +26432,7 @@
         <v>0</v>
       </c>
       <c r="AI218" s="3" t="n">
-        <v>46089.57291666666</v>
+        <v>46089.58333333334</v>
       </c>
     </row>
     <row r="219">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26896,10 +26896,10 @@
         <v>0</v>
       </c>
       <c r="AE222" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF222" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27155,27 +27155,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27265,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="AI225" s="3" t="n">
-        <v>46089.58333333334</v>
+        <v>46089.59375</v>
       </c>
     </row>
     <row r="226">
@@ -27274,12 +27274,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27384,7 +27384,7 @@
         <v>0</v>
       </c>
       <c r="AI226" s="3" t="n">
-        <v>46089.58333333334</v>
+        <v>46089.60416666666</v>
       </c>
     </row>
     <row r="227">
@@ -27393,27 +27393,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27503,7 +27503,7 @@
         <v>0</v>
       </c>
       <c r="AI227" s="3" t="n">
-        <v>46089.59375</v>
+        <v>46089.60416666666</v>
       </c>
     </row>
     <row r="228">
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -27598,10 +27598,10 @@
         <v>0</v>
       </c>
       <c r="AA228" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28345,12 +28345,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28455,7 +28455,7 @@
         <v>0</v>
       </c>
       <c r="AI235" s="3" t="n">
-        <v>46089.60416666666</v>
+        <v>46089.625</v>
       </c>
     </row>
     <row r="236">
@@ -28464,12 +28464,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="M236" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N236" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28574,7 +28574,7 @@
         <v>0</v>
       </c>
       <c r="AI236" s="3" t="n">
-        <v>46089.60416666666</v>
+        <v>46089.625</v>
       </c>
     </row>
     <row r="237">
@@ -28583,12 +28583,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28693,7 +28693,7 @@
         <v>0</v>
       </c>
       <c r="AI237" s="3" t="n">
-        <v>46089.625</v>
+        <v>46089.63541666666</v>
       </c>
     </row>
     <row r="238">
@@ -28702,12 +28702,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2.42</v>
+        <v>5.41</v>
       </c>
       <c r="M238" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="N238" t="n">
-        <v>2.97</v>
+        <v>1.53</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28812,7 +28812,7 @@
         <v>0</v>
       </c>
       <c r="AI238" s="3" t="n">
-        <v>46089.625</v>
+        <v>46089.63541666666</v>
       </c>
     </row>
     <row r="239">
@@ -28940,12 +28940,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29050,7 +29050,7 @@
         <v>0</v>
       </c>
       <c r="AI240" s="3" t="n">
-        <v>46089.63541666666</v>
+        <v>46089.64583333334</v>
       </c>
     </row>
     <row r="241">
@@ -29059,27 +29059,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29169,7 +29169,7 @@
         <v>0</v>
       </c>
       <c r="AI241" s="3" t="n">
-        <v>46089.63541666666</v>
+        <v>46089.64583333334</v>
       </c>
     </row>
     <row r="242">
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29297,27 +29297,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29407,7 +29407,7 @@
         <v>0</v>
       </c>
       <c r="AI243" s="3" t="n">
-        <v>46089.64583333334</v>
+        <v>46089.66666666666</v>
       </c>
     </row>
     <row r="244">
@@ -29416,27 +29416,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="AI244" s="3" t="n">
-        <v>46089.64583333334</v>
+        <v>46089.66666666666</v>
       </c>
     </row>
     <row r="245">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30011,12 +30011,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="M249" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="N249" t="n">
-        <v>3.48</v>
+        <v>4.34</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30121,7 +30121,7 @@
         <v>0</v>
       </c>
       <c r="AI249" s="3" t="n">
-        <v>46089.66666666666</v>
+        <v>46089.67708333334</v>
       </c>
     </row>
     <row r="250">
@@ -30130,27 +30130,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30240,7 +30240,7 @@
         <v>0</v>
       </c>
       <c r="AI250" s="3" t="n">
-        <v>46089.66666666666</v>
+        <v>46089.6875</v>
       </c>
     </row>
     <row r="251">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="AI251" s="3" t="n">
-        <v>46089.67708333334</v>
+        <v>46089.6875</v>
       </c>
     </row>
     <row r="252">
@@ -30368,12 +30368,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30478,7 +30478,7 @@
         <v>0</v>
       </c>
       <c r="AI252" s="3" t="n">
-        <v>46089.6875</v>
+        <v>46089.69791666666</v>
       </c>
     </row>
     <row r="253">
@@ -30487,12 +30487,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB253" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30585,10 +30585,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF253" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -30597,7 +30597,7 @@
         <v>0</v>
       </c>
       <c r="AI253" s="3" t="n">
-        <v>46089.6875</v>
+        <v>46089.69791666666</v>
       </c>
     </row>
     <row r="254">
@@ -30606,27 +30606,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30643,17 +30643,17 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30692,10 +30692,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -30716,7 +30716,7 @@
         <v>0</v>
       </c>
       <c r="AI254" s="3" t="n">
-        <v>46089.69791666666</v>
+        <v>46089.70833333334</v>
       </c>
     </row>
     <row r="255">
@@ -30725,12 +30725,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30766,13 +30766,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -30811,10 +30811,10 @@
         <v>0</v>
       </c>
       <c r="AA255" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB255" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC255" t="n">
         <v>0</v>
@@ -30823,10 +30823,10 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF255" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG255" t="n">
         <v>0</v>
@@ -30835,7 +30835,7 @@
         <v>0</v>
       </c>
       <c r="AI255" s="3" t="n">
-        <v>46089.69791666666</v>
+        <v>46089.70833333334</v>
       </c>
     </row>
     <row r="256">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -31201,12 +31201,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31311,7 +31311,7 @@
         <v>0</v>
       </c>
       <c r="AI259" s="3" t="n">
-        <v>46089.70833333334</v>
+        <v>46089.72916666666</v>
       </c>
     </row>
     <row r="260">
@@ -31320,12 +31320,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31430,7 +31430,7 @@
         <v>0</v>
       </c>
       <c r="AI260" s="3" t="n">
-        <v>46089.70833333334</v>
+        <v>46089.72916666666</v>
       </c>
     </row>
     <row r="261">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31915,7 +31915,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32025,7 +32025,7 @@
         <v>0</v>
       </c>
       <c r="AI265" s="3" t="n">
-        <v>46089.72916666666</v>
+        <v>46089.75</v>
       </c>
     </row>
     <row r="266">
@@ -32034,12 +32034,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32071,17 +32071,17 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
         <v>0</v>
       </c>
       <c r="AA266" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB266" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC266" t="n">
         <v>0</v>
@@ -32144,7 +32144,7 @@
         <v>0</v>
       </c>
       <c r="AI266" s="3" t="n">
-        <v>46089.72916666666</v>
+        <v>46089.75</v>
       </c>
     </row>
     <row r="267">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L267" t="n">
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32629,12 +32629,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L271" t="n">
@@ -32739,7 +32739,7 @@
         <v>0</v>
       </c>
       <c r="AI271" s="3" t="n">
-        <v>46089.75</v>
+        <v>46089.79166666666</v>
       </c>
     </row>
     <row r="272">
@@ -32748,27 +32748,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32858,7 +32858,7 @@
         <v>0</v>
       </c>
       <c r="AI272" s="3" t="n">
-        <v>46089.75</v>
+        <v>46089.79166666666</v>
       </c>
     </row>
     <row r="273">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32953,10 +32953,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB273" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC273" t="n">
         <v>0</v>
@@ -32991,22 +32991,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33224,27 +33224,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33334,7 +33334,7 @@
         <v>0</v>
       </c>
       <c r="AI276" s="3" t="n">
-        <v>46089.79166666666</v>
+        <v>46089.83333333334</v>
       </c>
     </row>
     <row r="277">
@@ -33343,12 +33343,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L277" t="n">
@@ -33453,7 +33453,7 @@
         <v>0</v>
       </c>
       <c r="AI277" s="3" t="n">
-        <v>46089.79166666666</v>
+        <v>46089.83333333334</v>
       </c>
     </row>
     <row r="278">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L280" t="n">
@@ -33819,12 +33819,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33929,7 +33929,7 @@
         <v>0</v>
       </c>
       <c r="AI281" s="3" t="n">
-        <v>46089.83333333334</v>
+        <v>46089.85416666666</v>
       </c>
     </row>
     <row r="282">
@@ -33938,27 +33938,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34048,7 +34048,7 @@
         <v>0</v>
       </c>
       <c r="AI282" s="3" t="n">
-        <v>46089.83333333334</v>
+        <v>46089.875</v>
       </c>
     </row>
     <row r="283">
@@ -34057,27 +34057,27 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34167,7 +34167,7 @@
         <v>0</v>
       </c>
       <c r="AI283" s="3" t="n">
-        <v>46089.85416666666</v>
+        <v>46089.875</v>
       </c>
     </row>
     <row r="284">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34524,7 +34524,7 @@
         <v>0</v>
       </c>
       <c r="AI286" s="3" t="n">
-        <v>46089.875</v>
+        <v>46089.89583333334</v>
       </c>
     </row>
     <row r="287">
@@ -34533,7 +34533,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34643,7 +34643,7 @@
         <v>0</v>
       </c>
       <c r="AI287" s="3" t="n">
-        <v>46089.875</v>
+        <v>46089.89583333334</v>
       </c>
     </row>
     <row r="288">
@@ -34652,27 +34652,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34762,244 +34762,6 @@
         <v>0</v>
       </c>
       <c r="AI288" s="3" t="n">
-        <v>46089.89583333334</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Austin II</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="G289" t="n">
-        <v>0</v>
-      </c>
-      <c r="H289" t="n">
-        <v>0</v>
-      </c>
-      <c r="I289" t="n">
-        <v>0</v>
-      </c>
-      <c r="J289" t="n">
-        <v>0</v>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L289" t="n">
-        <v>0</v>
-      </c>
-      <c r="M289" t="n">
-        <v>0</v>
-      </c>
-      <c r="N289" t="n">
-        <v>0</v>
-      </c>
-      <c r="O289" t="n">
-        <v>0</v>
-      </c>
-      <c r="P289" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
-      <c r="R289" t="n">
-        <v>0</v>
-      </c>
-      <c r="S289" t="n">
-        <v>0</v>
-      </c>
-      <c r="T289" t="n">
-        <v>0</v>
-      </c>
-      <c r="U289" t="n">
-        <v>0</v>
-      </c>
-      <c r="V289" t="n">
-        <v>0</v>
-      </c>
-      <c r="W289" t="n">
-        <v>0</v>
-      </c>
-      <c r="X289" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y289" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH289" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI289" s="3" t="n">
-        <v>46089.89583333334</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="n">
-        <v>46089</v>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes II</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Los Angeles II</t>
-        </is>
-      </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>0</v>
-      </c>
-      <c r="I290" t="n">
-        <v>0</v>
-      </c>
-      <c r="J290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L290" t="n">
-        <v>0</v>
-      </c>
-      <c r="M290" t="n">
-        <v>0</v>
-      </c>
-      <c r="N290" t="n">
-        <v>0</v>
-      </c>
-      <c r="O290" t="n">
-        <v>0</v>
-      </c>
-      <c r="P290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
-      <c r="R290" t="n">
-        <v>0</v>
-      </c>
-      <c r="S290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U290" t="n">
-        <v>0</v>
-      </c>
-      <c r="V290" t="n">
-        <v>0</v>
-      </c>
-      <c r="W290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI290" s="3" t="n">
         <v>46089.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -900,10 +900,10 @@
         <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>1.94</v>
+        <v>3.48</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8834,22 +8834,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,22 +8953,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>3.64</v>
+        <v>4.35</v>
       </c>
       <c r="N75" t="n">
-        <v>2.54</v>
+        <v>5.22</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>5.1</v>
+        <v>1.42</v>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N76" t="n">
-        <v>1.51</v>
+        <v>6.54</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9516,10 +9516,10 @@
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE76" t="n">
         <v>0</v>
@@ -9548,22 +9548,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.42</v>
+        <v>2.48</v>
       </c>
       <c r="M80" t="n">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="N80" t="n">
-        <v>6.54</v>
+        <v>2.54</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,16 +9986,16 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,22 +10262,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="M96" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>4.27</v>
+        <v>2.12</v>
       </c>
       <c r="M99" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="N99" t="n">
-        <v>1.82</v>
+        <v>3.45</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.12</v>
+        <v>4.27</v>
       </c>
       <c r="M107" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N107" t="n">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.95</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="N112" t="n">
-        <v>2.07</v>
+        <v>4.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13806,10 +13806,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="M114" t="n">
-        <v>6.71</v>
+        <v>3.7</v>
       </c>
       <c r="N114" t="n">
-        <v>11.6</v>
+        <v>5.03</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14871,10 +14871,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="M123" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N123" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.67</v>
+        <v>2.21</v>
       </c>
       <c r="M125" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="N125" t="n">
-        <v>5.03</v>
+        <v>3.02</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.52</v>
+        <v>24</v>
       </c>
       <c r="M126" t="n">
-        <v>4.19</v>
+        <v>10.2</v>
       </c>
       <c r="N126" t="n">
-        <v>7.01</v>
+        <v>1.06</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.7</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
       <c r="N127" t="n">
-        <v>4.9</v>
+        <v>2.07</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="M148" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N148" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,22 +18354,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,22 +18711,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,22 +19068,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="M170" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="N170" t="n">
-        <v>2.34</v>
+        <v>3.52</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.46</v>
+        <v>1.45</v>
       </c>
       <c r="M182" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N182" t="n">
-        <v>2.43</v>
+        <v>6.9</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.32</v>
+        <v>4.33</v>
       </c>
       <c r="M185" t="n">
-        <v>4.8</v>
+        <v>3.91</v>
       </c>
       <c r="N185" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="M188" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="N188" t="n">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M190" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N190" t="n">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="M195" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="N195" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="M203" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N203" t="n">
-        <v>2.57</v>
+        <v>4.27</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AB203" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="M205" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N205" t="n">
-        <v>4.27</v>
+        <v>2.57</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="M212" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="N212" t="n">
-        <v>4.19</v>
+        <v>3.26</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="M213" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="N213" t="n">
-        <v>3.26</v>
+        <v>4.19</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.18</v>
+        <v>3.34</v>
       </c>
       <c r="M214" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N214" t="n">
-        <v>3.66</v>
+        <v>2.02</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26301,10 +26301,10 @@
         <v>0</v>
       </c>
       <c r="AE217" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF217" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>4.4</v>
+        <v>1.97</v>
       </c>
       <c r="M227" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="N227" t="n">
-        <v>1.67</v>
+        <v>3.65</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="M228" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="N228" t="n">
-        <v>3.65</v>
+        <v>1.67</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -27598,10 +27598,10 @@
         <v>0</v>
       </c>
       <c r="AA228" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="M235" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N235" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="M236" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N236" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28669,10 +28669,10 @@
         <v>0</v>
       </c>
       <c r="AA237" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB237" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC237" t="n">
         <v>0</v>
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="M252" t="n">
-        <v>4.37</v>
+        <v>2.95</v>
       </c>
       <c r="N252" t="n">
-        <v>6.25</v>
+        <v>2.21</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30466,10 +30466,10 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF252" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG252" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="M253" t="n">
-        <v>2.95</v>
+        <v>4.37</v>
       </c>
       <c r="N253" t="n">
-        <v>2.21</v>
+        <v>6.25</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30573,10 +30573,10 @@
         <v>0</v>
       </c>
       <c r="AA253" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB253" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC253" t="n">
         <v>0</v>
@@ -30585,10 +30585,10 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF253" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L254" t="n">
@@ -30730,22 +30730,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30762,7 +30762,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L255" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.68</v>
+        <v>2.49</v>
       </c>
       <c r="M260" t="n">
-        <v>4.26</v>
+        <v>3.18</v>
       </c>
       <c r="N260" t="n">
-        <v>4.99</v>
+        <v>3.18</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31763,10 +31763,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32071,7 +32071,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32309,7 +32309,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -32406,12 +32406,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,22 +32515,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L280" t="n">
@@ -33943,22 +33943,22 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34300,22 +34300,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34419,22 +34419,22 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,22 +34538,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G287" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -662,10 +662,10 @@
         <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,22 +8477,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9310,22 +9310,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>3.6</v>
+        <v>4.35</v>
       </c>
       <c r="N76" t="n">
-        <v>3.3</v>
+        <v>5.22</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,22 +9667,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="N79" t="n">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="O79" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.19</v>
+        <v>1.63</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46089.39583333334</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="M80" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46089.39583333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="M82" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="N82" t="n">
-        <v>5.22</v>
+        <v>6.54</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,16 +10224,16 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4.27</v>
+        <v>2.13</v>
       </c>
       <c r="M104" t="n">
-        <v>3.89</v>
+        <v>3.32</v>
       </c>
       <c r="N104" t="n">
-        <v>1.82</v>
+        <v>3.04</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="M113" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N113" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.95</v>
+        <v>1.52</v>
       </c>
       <c r="M116" t="n">
-        <v>3.59</v>
+        <v>4.19</v>
       </c>
       <c r="N116" t="n">
-        <v>2.07</v>
+        <v>7.01</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="N117" t="n">
-        <v>3.02</v>
+        <v>4.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14401,10 +14401,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="M118" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="N118" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="M121" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N121" t="n">
-        <v>5.03</v>
+        <v>3.31</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="M122" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N122" t="n">
-        <v>3.71</v>
+        <v>3.02</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15109,10 +15109,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="M124" t="n">
-        <v>3.7</v>
+        <v>6.71</v>
       </c>
       <c r="N124" t="n">
-        <v>4.9</v>
+        <v>11.6</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,22 +15222,22 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.08</v>
+        <v>24</v>
       </c>
       <c r="M126" t="n">
-        <v>3.45</v>
+        <v>10.2</v>
       </c>
       <c r="N126" t="n">
-        <v>3.31</v>
+        <v>1.06</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,73 +16843,73 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.89</v>
+        <v>2.85</v>
       </c>
       <c r="M138" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N138" t="n">
-        <v>3.99</v>
+        <v>2.34</v>
       </c>
       <c r="O138" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V138" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W138" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X138" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD138" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH138" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
         <v>46089.5</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,73 +16962,73 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="M139" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N139" t="n">
-        <v>2.58</v>
+        <v>3.99</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S139" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V139" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W139" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC139" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD139" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG139" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH139" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI139" s="3" t="n">
         <v>46089.5</v>
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,22 +18473,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,22 +19187,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,22 +20972,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.46</v>
+        <v>4.14</v>
       </c>
       <c r="M180" t="n">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="N180" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.33</v>
+        <v>1.32</v>
       </c>
       <c r="M187" t="n">
-        <v>3.91</v>
+        <v>4.8</v>
       </c>
       <c r="N187" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,22 +22757,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.76</v>
+        <v>3.32</v>
       </c>
       <c r="M196" t="n">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="N196" t="n">
-        <v>4.3</v>
+        <v>2.07</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="M199" t="n">
-        <v>3.18</v>
+        <v>3.57</v>
       </c>
       <c r="N199" t="n">
-        <v>3.09</v>
+        <v>4.62</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="M201" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="N201" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>3.32</v>
+        <v>1.76</v>
       </c>
       <c r="M202" t="n">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="N202" t="n">
-        <v>2.07</v>
+        <v>4.3</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.9</v>
+        <v>3.56</v>
       </c>
       <c r="M204" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="N204" t="n">
-        <v>2.57</v>
+        <v>2.02</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="M205" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N205" t="n">
-        <v>4.27</v>
+        <v>2.57</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>3.56</v>
+        <v>1.97</v>
       </c>
       <c r="M206" t="n">
-        <v>3.35</v>
+        <v>3.66</v>
       </c>
       <c r="N206" t="n">
-        <v>2.02</v>
+        <v>4.27</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.34</v>
+        <v>2.18</v>
       </c>
       <c r="M208" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N208" t="n">
-        <v>2.02</v>
+        <v>3.66</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.75</v>
+        <v>3.34</v>
       </c>
       <c r="M209" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N209" t="n">
-        <v>4.19</v>
+        <v>2.02</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="M224" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N224" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="AB224" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27134,10 +27134,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF224" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="M226" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N226" t="n">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.37</v>
+        <v>2.03</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27372,10 +27372,10 @@
         <v>0</v>
       </c>
       <c r="AE226" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF226" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>2.59</v>
+        <v>4.4</v>
       </c>
       <c r="M228" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="N228" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="M229" t="n">
-        <v>3.57</v>
+        <v>2.88</v>
       </c>
       <c r="N229" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="M234" t="n">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="N234" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28312,10 +28312,10 @@
         <v>0</v>
       </c>
       <c r="AA234" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC234" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>5.41</v>
+        <v>1.95</v>
       </c>
       <c r="M241" t="n">
-        <v>4.25</v>
+        <v>3.79</v>
       </c>
       <c r="N241" t="n">
-        <v>1.53</v>
+        <v>3.71</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29145,10 +29145,10 @@
         <v>0</v>
       </c>
       <c r="AA241" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB241" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.09</v>
+        <v>1.33</v>
       </c>
       <c r="M247" t="n">
-        <v>3.32</v>
+        <v>5.81</v>
       </c>
       <c r="N247" t="n">
-        <v>3.48</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31000,7 +31000,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L257" t="n">
@@ -31087,22 +31087,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L258" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.68</v>
+        <v>2.49</v>
       </c>
       <c r="M262" t="n">
-        <v>4.26</v>
+        <v>3.18</v>
       </c>
       <c r="N262" t="n">
-        <v>4.99</v>
+        <v>3.18</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.49</v>
+        <v>1.68</v>
       </c>
       <c r="M267" t="n">
-        <v>3.18</v>
+        <v>4.26</v>
       </c>
       <c r="N267" t="n">
-        <v>3.18</v>
+        <v>4.99</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32239,10 +32239,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB267" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32396,22 +32396,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -32515,7 +32515,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -32525,12 +32525,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -32547,7 +32547,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L270" t="n">
@@ -32753,22 +32753,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,22 +32872,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33023,17 +33023,17 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33072,10 +33072,10 @@
         <v>0</v>
       </c>
       <c r="AA274" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB274" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC274" t="n">
         <v>0</v>
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33499,17 +33499,17 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB278" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33586,7 +33586,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -33596,12 +33596,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -33618,7 +33618,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L279" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33856,7 +33856,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L281" t="n">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34538,22 +34538,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,22 +34657,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,22 +34776,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34895,22 +34895,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G290" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -662,10 +662,10 @@
         <v>2.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -900,10 +900,10 @@
         <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>1.94</v>
+        <v>3.48</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3717,22 +3717,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,22 +3836,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.66</v>
+        <v>3.09</v>
       </c>
       <c r="M57" t="n">
-        <v>4.32</v>
+        <v>3.48</v>
       </c>
       <c r="N57" t="n">
-        <v>4.79</v>
+        <v>2.16</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N66" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -8358,22 +8358,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,22 +9191,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="M77" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="N77" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="M79" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="N79" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46089.39583333334</v>
@@ -10024,22 +10024,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46089.39583333334</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="N83" t="n">
-        <v>1.51</v>
+        <v>5.22</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,22 +11214,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="M92" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.12</v>
+        <v>4.27</v>
       </c>
       <c r="M100" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="N100" t="n">
-        <v>3.45</v>
+        <v>1.82</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="M113" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N113" t="n">
-        <v>2.65</v>
+        <v>3.31</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.52</v>
+        <v>24</v>
       </c>
       <c r="M116" t="n">
-        <v>4.19</v>
+        <v>10.2</v>
       </c>
       <c r="N116" t="n">
-        <v>7.01</v>
+        <v>1.06</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14401,10 +14401,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,22 +14546,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.21</v>
+        <v>1.28</v>
       </c>
       <c r="M122" t="n">
-        <v>3.16</v>
+        <v>6.71</v>
       </c>
       <c r="N122" t="n">
-        <v>3.02</v>
+        <v>11.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,16 +14984,16 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15228,10 +15228,10 @@
         <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>24</v>
+        <v>2.6</v>
       </c>
       <c r="M126" t="n">
-        <v>10.2</v>
+        <v>3.2</v>
       </c>
       <c r="N126" t="n">
-        <v>1.06</v>
+        <v>2.65</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.42</v>
+        <v>1.7</v>
       </c>
       <c r="M128" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N128" t="n">
-        <v>2.94</v>
+        <v>4.9</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15710,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="M129" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N129" t="n">
-        <v>3.71</v>
+        <v>3.02</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="M137" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="N137" t="n">
-        <v>3.52</v>
+        <v>2.34</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,73 +16962,73 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V139" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W139" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD139" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
         <v>46089.5</v>
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,22 +19187,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,73 +19342,73 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V159" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W159" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X159" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE159" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF159" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG159" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH159" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI159" s="3" t="n">
         <v>46089.5</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="M172" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="N172" t="n">
-        <v>2.55</v>
+        <v>4.77</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,22 +21329,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="M181" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N181" t="n">
-        <v>6.9</v>
+        <v>2.43</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.46</v>
+        <v>1.45</v>
       </c>
       <c r="M183" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N183" t="n">
-        <v>2.43</v>
+        <v>6.9</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="M193" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="N193" t="n">
-        <v>3.09</v>
+        <v>3.37</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2.04</v>
+        <v>3.32</v>
       </c>
       <c r="M195" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N195" t="n">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23709,22 +23709,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.32</v>
+        <v>1.75</v>
       </c>
       <c r="M196" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="N196" t="n">
-        <v>2.07</v>
+        <v>4.62</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.76</v>
+        <v>2.41</v>
       </c>
       <c r="M202" t="n">
-        <v>3.74</v>
+        <v>3.16</v>
       </c>
       <c r="N202" t="n">
-        <v>4.3</v>
+        <v>2.97</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24504,10 +24504,10 @@
         <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M204" t="n">
         <v>3.56</v>
       </c>
-      <c r="M204" t="n">
-        <v>3.35</v>
-      </c>
       <c r="N204" t="n">
-        <v>2.02</v>
+        <v>2.57</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="M205" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N205" t="n">
-        <v>2.57</v>
+        <v>4.27</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.61</v>
+        <v>2.01</v>
       </c>
       <c r="AB205" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="M206" t="n">
-        <v>3.66</v>
+        <v>4.17</v>
       </c>
       <c r="N206" t="n">
-        <v>4.27</v>
+        <v>5.28</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.71</v>
+        <v>3.56</v>
       </c>
       <c r="M207" t="n">
-        <v>4.17</v>
+        <v>3.35</v>
       </c>
       <c r="N207" t="n">
-        <v>5.28</v>
+        <v>2.02</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.34</v>
+        <v>1.75</v>
       </c>
       <c r="M209" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N209" t="n">
-        <v>2.02</v>
+        <v>4.19</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="M212" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="N212" t="n">
-        <v>4.19</v>
+        <v>3.26</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="M213" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="N213" t="n">
-        <v>3.26</v>
+        <v>2.02</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>0</v>
       </c>
       <c r="AE221" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF221" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27134,10 +27134,10 @@
         <v>0</v>
       </c>
       <c r="AE224" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF224" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.65</v>
+        <v>1.64</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>4.88</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.64</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
         <v>3.52</v>
       </c>
       <c r="N10" t="n">
-        <v>4.88</v>
+        <v>2.36</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="N12" t="n">
-        <v>1.94</v>
+        <v>2.72</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>3.48</v>
+        <v>1.94</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.59</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.09</v>
+        <v>1.66</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>4.32</v>
       </c>
       <c r="N57" t="n">
-        <v>2.16</v>
+        <v>4.79</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="N61" t="n">
-        <v>3.24</v>
+        <v>4.02</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8213,10 +8213,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,22 +8715,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,22 +8953,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="N78" t="n">
-        <v>3.8</v>
+        <v>5.22</v>
       </c>
       <c r="O78" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AC78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46089.39583333334</v>
@@ -9786,22 +9786,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="M81" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.54</v>
+        <v>1.51</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="M82" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="N82" t="n">
-        <v>5.22</v>
+        <v>3.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,73 +10298,73 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
       <c r="M83" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>6.54</v>
+        <v>3.8</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC83" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>46089.39583333334</v>
@@ -10381,22 +10381,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>8.199999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="M85" t="n">
-        <v>5.2</v>
+        <v>3.64</v>
       </c>
       <c r="N85" t="n">
-        <v>1.28</v>
+        <v>2.54</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>5.1</v>
+        <v>1.42</v>
       </c>
       <c r="M86" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="N86" t="n">
-        <v>1.51</v>
+        <v>6.54</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="M116" t="n">
-        <v>3.7</v>
+        <v>4.19</v>
       </c>
       <c r="N116" t="n">
-        <v>4.9</v>
+        <v>7.01</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14282,10 +14282,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14401,10 +14401,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="M120" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="N120" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="M121" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N121" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="M122" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N122" t="n">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.97</v>
+        <v>4.18</v>
       </c>
       <c r="M137" t="n">
-        <v>3.6</v>
+        <v>3.03</v>
       </c>
       <c r="N137" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.18</v>
+        <v>2.97</v>
       </c>
       <c r="M138" t="n">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="N138" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="M149" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N149" t="n">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,22 +18235,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -19187,22 +19187,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="M222" t="n">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="N222" t="n">
-        <v>2.19</v>
+        <v>4.58</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27360,10 +27360,10 @@
         <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -27527,12 +27527,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -27553,13 +27553,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.01</v>
+        <v>2.59</v>
       </c>
       <c r="M231" t="n">
-        <v>3.93</v>
+        <v>2.78</v>
       </c>
       <c r="N231" t="n">
-        <v>3.46</v>
+        <v>2.84</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="M232" t="n">
-        <v>2.88</v>
+        <v>3.93</v>
       </c>
       <c r="N232" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28148,13 +28148,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="M233" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="N233" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28431,10 +28431,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28624,13 +28624,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -28669,10 +28669,10 @@
         <v>0</v>
       </c>
       <c r="AA237" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC237" t="n">
         <v>0</v>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,73 +28981,73 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="M240" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N240" t="n">
         <v>3.1</v>
       </c>
-      <c r="N240" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O240" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T240" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V240" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W240" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X240" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD240" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF240" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG240" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH240" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI240" s="3" t="n">
         <v>46089.625</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,73 +29219,73 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="M242" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N242" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O242" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P242" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R242" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S242" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T242" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U242" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V242" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X242" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z242" t="n">
         <v>3.15</v>
       </c>
-      <c r="N242" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="P242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="n">
-        <v>0</v>
-      </c>
-      <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="n">
-        <v>0</v>
-      </c>
-      <c r="V242" t="n">
-        <v>0</v>
-      </c>
-      <c r="W242" t="n">
-        <v>0</v>
-      </c>
-      <c r="X242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z242" t="n">
-        <v>0</v>
-      </c>
       <c r="AA242" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB242" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC242" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD242" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE242" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF242" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG242" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH242" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI242" s="3" t="n">
         <v>46089.625</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29502,10 +29502,10 @@
         <v>0</v>
       </c>
       <c r="AA244" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC244" t="n">
         <v>0</v>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>5.41</v>
+        <v>1.95</v>
       </c>
       <c r="M245" t="n">
-        <v>4.25</v>
+        <v>3.79</v>
       </c>
       <c r="N245" t="n">
-        <v>1.53</v>
+        <v>3.71</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29621,10 +29621,10 @@
         <v>0</v>
       </c>
       <c r="AA245" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC245" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="M247" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N247" t="n">
-        <v>3.27</v>
+        <v>4.57</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M248" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N248" t="n">
         <v>3.27</v>
-      </c>
-      <c r="N248" t="n">
-        <v>4.57</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -30383,12 +30383,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30454,10 +30454,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>1.33</v>
+        <v>2.09</v>
       </c>
       <c r="M253" t="n">
-        <v>5.81</v>
+        <v>3.32</v>
       </c>
       <c r="N253" t="n">
-        <v>8.449999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30692,10 +30692,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -30730,22 +30730,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G255" t="n">

--- a/jogos_2026-03-08.xlsx
+++ b/jogos_2026-03-08.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N8" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>3.48</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,22 +2408,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
